--- a/questionnaire_templates/003_patient_health_questionnaire_phq9--questionnaire_templates.xlsx
+++ b/questionnaire_templates/003_patient_health_questionnaire_phq9--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,7 +520,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_1</t>
+          <t>general_symptoms</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,7 +543,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_2</t>
+          <t>physical_health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,41 +566,41 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_3</t>
+          <t>social_relationships</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Psychological Health</t>
+          <t>Social Relationships</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_4</t>
+          <t>emotional_state</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Social Relationships</t>
+          <t>Emotional State</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,64 +612,64 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_5</t>
+          <t>health_concerns</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Additional Health Information</t>
+          <t>Health Concerns</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_6</t>
+          <t>mental_health_history</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>General Symptoms</t>
+          <t>Mental Health History</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_7</t>
+          <t>physical_symptoms</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Physical Health</t>
+          <t>Physical Symptoms</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,18 +681,18 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_8</t>
+          <t>social_support</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Psychological Health</t>
+          <t>Social Support</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,386 +704,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_9</t>
+          <t>emotional_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Social Relationships</t>
+          <t>Emotional Support</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_10</t>
+          <t>mental_health_services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Additional Health Information</t>
+          <t>Mental Health Services</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_11</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>General Symptoms</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Physical Health</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_13</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Psychological Health</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Social Relationships</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Additional Health Information</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>General Symptoms</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Physical Health</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Psychological Health</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Social Relationships</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Health Information</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>General Symptoms</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Physical Health</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Psychological Health</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Social Relationships</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Additional Health Information</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,10 +753,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +781,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_1_choices</t>
+          <t>general_symptoms_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +798,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_1_choices</t>
+          <t>general_symptoms_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +815,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_2_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +832,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_2_choices</t>
+          <t>physical_health_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +849,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_3_choices</t>
+          <t>social_relationships_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,7 +866,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_3_choices</t>
+          <t>social_relationships_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1228,7 +883,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_4_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +900,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_4_choices</t>
+          <t>emotional_state_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +917,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_6_choices</t>
+          <t>mental_health_history_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +934,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_6_choices</t>
+          <t>mental_health_history_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +951,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_7_choices</t>
+          <t>physical_symptoms_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1313,7 +968,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_7_choices</t>
+          <t>physical_symptoms_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1330,7 +985,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_8_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1002,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_8_choices</t>
+          <t>social_support_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1019,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_9_choices</t>
+          <t>emotional_support_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1036,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_9_choices</t>
+          <t>emotional_support_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1398,7 +1053,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_11_choices</t>
+          <t>mental_health_services_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1415,7 +1070,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>patient_health_questionnaire_phq9_page_11_choices</t>
+          <t>mental_health_services_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1424,380 +1079,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_12_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_13_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_13_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_14_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>patient_health_questionnaire_phq9_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
         <is>
           <t>No</t>
         </is>
